--- a/Result/profitability/6534.xlsx
+++ b/Result/profitability/6534.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM40"/>
+  <dimension ref="A1:AM41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5510,6 +5510,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6534</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>459</v>
+      </c>
+      <c r="D41" t="n">
+        <v>70</v>
+      </c>
+      <c r="E41" t="n">
+        <v>390</v>
+      </c>
+      <c r="F41" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="G41" t="n">
+        <v>171</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>37.16%</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>167</v>
+      </c>
+      <c r="K41" t="n">
+        <v>151</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.18375</v>
+      </c>
+      <c r="N41" t="n">
+        <v>81.23125</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="X41" t="n">
+        <v>-0.6409638554216868</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-1.319999999999993</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-0.01531500174034106</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>3.027027027027027</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.930000000000007</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.02326983361466128</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
